--- a/assets/20260327批發表.xlsx
+++ b/assets/20260327批發表.xlsx
@@ -47901,7 +47901,7 @@
         <v>420495507288</v>
       </c>
       <c r="D987" s="6">
-        <v>5000</v>
+        <v>6300</v>
       </c>
       <c r="E987" s="7">
         <v>5</v>
